--- a/Data/RemapDrafts/ChangliRemapDraft.xlsx
+++ b/Data/RemapDrafts/ChangliRemapDraft.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -456,7 +456,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -471,7 +470,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -8854,14 +8852,14 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>259</v>
+        <v>92</v>
       </c>
       <c r="C242" t="n">
         <v>0.28</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>260 verts (Component 5) -&gt; 155 verts (Component 5), dist 4.3168; runner-up 258 at dist 11.4962</t>
+          <t>IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (259), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 260 verts (Component 5) -&gt; 155 verts (Component 5), dist 4.3168; runner-up 258 at dist 11.4962]</t>
         </is>
       </c>
     </row>
@@ -8870,14 +8868,14 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>258</v>
+        <v>93</v>
       </c>
       <c r="C243" t="n">
         <v>0.722</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>204 verts (Component 5) -&gt; 158 verts (Component 5), dist 8.4340; runner-up 259 at dist 9.6326</t>
+          <t>IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 204 verts (Component 5) -&gt; 158 verts (Component 5), dist 8.4340; runner-up 259 at dist 9.6326]</t>
         </is>
       </c>
     </row>
@@ -8886,14 +8884,14 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>258</v>
+        <v>93</v>
       </c>
       <c r="C244" t="n">
         <v>0.976</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>124 verts (Component 5) -&gt; 158 verts (Component 5), dist 9.4179; runner-up 259 at dist 13.1920</t>
+          <t>IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 124 verts (Component 5) -&gt; 158 verts (Component 5), dist 9.4179; runner-up 259 at dist 13.1920]</t>
         </is>
       </c>
     </row>
@@ -8998,14 +8996,14 @@
         <v>249</v>
       </c>
       <c r="B251" t="n">
-        <v>264</v>
+        <v>104</v>
       </c>
       <c r="C251" t="n">
         <v>0.28</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>260 verts (Component 5) -&gt; 155 verts (Component 5), dist 4.3168; runner-up 263 at dist 11.4962</t>
+          <t>IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (264), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 260 verts (Component 5) -&gt; 155 verts (Component 5), dist 4.3168; runner-up 263 at dist 11.4962]</t>
         </is>
       </c>
     </row>
@@ -9014,14 +9012,14 @@
         <v>250</v>
       </c>
       <c r="B252" t="n">
-        <v>263</v>
+        <v>105</v>
       </c>
       <c r="C252" t="n">
         <v>0.722</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>204 verts (Component 5) -&gt; 158 verts (Component 5), dist 8.4340; runner-up 264 at dist 9.6326</t>
+          <t>IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (263), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 204 verts (Component 5) -&gt; 158 verts (Component 5), dist 8.4340; runner-up 264 at dist 9.6326]</t>
         </is>
       </c>
     </row>
@@ -9030,14 +9028,14 @@
         <v>251</v>
       </c>
       <c r="B253" t="n">
-        <v>263</v>
+        <v>105</v>
       </c>
       <c r="C253" t="n">
         <v>0.976</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>124 verts (Component 5) -&gt; 158 verts (Component 5), dist 9.4179; runner-up 264 at dist 13.1920</t>
+          <t>IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (263), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 124 verts (Component 5) -&gt; 158 verts (Component 5), dist 9.4179; runner-up 264 at dist 13.1920]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/ChangliRemapDraft.xlsx
+++ b/Data/RemapDrafts/ChangliRemapDraft.xlsx
@@ -8852,14 +8852,14 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="C242" t="n">
         <v>0.28</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (259), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 260 verts (Component 5) -&gt; 155 verts (Component 5), dist 4.3168; runner-up 258 at dist 11.4962]</t>
+          <t>IN-GAME AUDIT (reverse epoch 3, 2026-10-21): the right side veil goes to Changli's right thigh (173), a rigid leg bone: her right dress panel (92 / 93, the buckle side) is turned in her idle and the veil hung edge-on on it (epoch 3; before that, 92). IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (259), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 260 verts (Component 5) -&gt; 155 verts (Component 5), dist 4.3168; runner-up 258 at dist 11.4962]</t>
         </is>
       </c>
     </row>
@@ -8868,14 +8868,14 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="C243" t="n">
         <v>0.722</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 204 verts (Component 5) -&gt; 158 verts (Component 5), dist 8.4340; runner-up 259 at dist 9.6326]</t>
+          <t>IN-GAME AUDIT (reverse epoch 3, 2026-10-21): the right side veil goes to Changli's right thigh (173), a rigid leg bone: her right dress panel (92 / 93, the buckle side) is turned in her idle and the veil hung edge-on on it (epoch 3; before that, 93). IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 204 verts (Component 5) -&gt; 158 verts (Component 5), dist 8.4340; runner-up 259 at dist 9.6326]</t>
         </is>
       </c>
     </row>
@@ -8884,14 +8884,14 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="C244" t="n">
         <v>0.976</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 124 verts (Component 5) -&gt; 158 verts (Component 5), dist 9.4179; runner-up 259 at dist 13.1920]</t>
+          <t>IN-GAME AUDIT (reverse epoch 3, 2026-10-21): the right side veil goes to Changli's right thigh (173), a rigid leg bone: her right dress panel (92 / 93, the buckle side) is turned in her idle and the veil hung edge-on on it (epoch 3; before that, 93). IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 124 verts (Component 5) -&gt; 158 verts (Component 5), dist 9.4179; runner-up 259 at dist 13.1920]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/ChangliRemapDraft.xlsx
+++ b/Data/RemapDrafts/ChangliRemapDraft.xlsx
@@ -8852,14 +8852,14 @@
         <v>240</v>
       </c>
       <c r="B242" t="n">
-        <v>173</v>
+        <v>92</v>
       </c>
       <c r="C242" t="n">
         <v>0.28</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>IN-GAME AUDIT (reverse epoch 3, 2026-10-21): the right side veil goes to Changli's right thigh (173), a rigid leg bone: her right dress panel (92 / 93, the buckle side) is turned in her idle and the veil hung edge-on on it (epoch 3; before that, 92). IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (259), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 260 verts (Component 5) -&gt; 155 verts (Component 5), dist 4.3168; runner-up 258 at dist 11.4962]</t>
+          <t>IN-GAME AUDIT (reverse epochs 3-4, 2026-10-21): kept on Changli's right dress side panel, the mirror of the left veil. Seen from straight in front her right side panel is edge-on on Changli and broad on the skin's card: both panels are modelled facing sideways and the skin's idle turns the right one to the front. Her right thigh (173) and pelvis (170) left it edge-on just the same. IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (259), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 260 verts (Component 5) -&gt; 155 verts (Component 5), dist 4.3168; runner-up 258 at dist 11.4962]</t>
         </is>
       </c>
     </row>
@@ -8868,14 +8868,14 @@
         <v>241</v>
       </c>
       <c r="B243" t="n">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="C243" t="n">
         <v>0.722</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>IN-GAME AUDIT (reverse epoch 3, 2026-10-21): the right side veil goes to Changli's right thigh (173), a rigid leg bone: her right dress panel (92 / 93, the buckle side) is turned in her idle and the veil hung edge-on on it (epoch 3; before that, 93). IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 204 verts (Component 5) -&gt; 158 verts (Component 5), dist 8.4340; runner-up 259 at dist 9.6326]</t>
+          <t>IN-GAME AUDIT (reverse epochs 3-4, 2026-10-21): kept on Changli's right dress side panel, the mirror of the left veil. Seen from straight in front her right side panel is edge-on on Changli and broad on the skin's card: both panels are modelled facing sideways and the skin's idle turns the right one to the front. Her right thigh (173) and pelvis (170) left it edge-on just the same. IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 204 verts (Component 5) -&gt; 158 verts (Component 5), dist 8.4340; runner-up 259 at dist 9.6326]</t>
         </is>
       </c>
     </row>
@@ -8884,14 +8884,14 @@
         <v>242</v>
       </c>
       <c r="B244" t="n">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="C244" t="n">
         <v>0.976</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>IN-GAME AUDIT (reverse epoch 3, 2026-10-21): the right side veil goes to Changli's right thigh (173), a rigid leg bone: her right dress panel (92 / 93, the buckle side) is turned in her idle and the veil hung edge-on on it (epoch 3; before that, 93). IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 124 verts (Component 5) -&gt; 158 verts (Component 5), dist 9.4179; runner-up 259 at dist 13.1920]</t>
+          <t>IN-GAME AUDIT (reverse epochs 3-4, 2026-10-21): kept on Changli's right dress side panel, the mirror of the left veil. Seen from straight in front her right side panel is edge-on on Changli and broad on the skin's card: both panels are modelled facing sideways and the skin's idle turns the right one to the front. Her right thigh (173) and pelvis (170) left it edge-on just the same. IN-GAME AUDIT (reverse epoch 2, 2026-10-21): her side-veil chain goes to Changli's dress side-panel chain, not the coat sash it was mapped to (258), which swings free -- the veil peeled off her hip and hung in mid-air. [before: 124 verts (Component 5) -&gt; 158 verts (Component 5), dist 9.4179; runner-up 259 at dist 13.1920]</t>
         </is>
       </c>
     </row>

--- a/Data/RemapDrafts/ChangliRemapDraft.xlsx
+++ b/Data/RemapDrafts/ChangliRemapDraft.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -470,9 +470,17 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>🔥🎭 The Borrowed Shader Smith: The 68th member of The Council</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
